--- a/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
@@ -656,7 +656,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1309,9 +1309,8 @@
     <row r="23"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
@@ -667,7 +667,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/ESG - SR26 sustainability reporting request.xlsx
@@ -767,9 +767,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -828,7 +828,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -867,7 +868,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -935,17 +936,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -977,17 +968,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -1049,8 +1030,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1111,8 +1090,6 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="154" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
@@ -1163,8 +1140,6 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
@@ -1209,8 +1184,6 @@
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
@@ -1255,10 +1228,8 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="171" customHeight="1">
+    </row>
+    <row r="21" ht="154" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
@@ -1281,13 +1252,13 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
+          <t>Please provide examples of internal engagement or external partnerships involving your portfolio that contributed to sustainability outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
 In end-2025 reporting your area reported on the related SP2030 target 7a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -1311,8 +1282,6 @@
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
@@ -1337,7 +1306,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
+          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -1357,23 +1326,16 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="15" t="n"/>
     </row>
     <row r="23"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B29"/>
     <hyperlink ref="H17" location="'3. SR25 responses'!B28"/>
